--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260713.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260713.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>531,048,578</t>
+          <t>532,033,177</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>58.31%</t>
+          <t>58.72%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>32,087,333</t>
+          <t>32,146,777</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>5.73%</t>
+          <t>5.56%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>41,986,024</t>
+          <t>42,064,025</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.60%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>265,305,613</t>
+          <t>265,799,106</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>72,162,102</t>
+          <t>72,296,159</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>253,939,947</t>
+          <t>254,411,341</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>6,323,399</t>
+          <t>6,334,949</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -765,78 +765,78 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>34,275,552</t>
+          <t>34,339,154</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>385,955,331</t>
+          <t>10,843,078</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>10,823,058</t>
+          <t>28,716,363</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>28,663,079</t>
+          <t>386,771,276</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>181,244,236</t>
+          <t>181,682,265</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -875,56 +875,56 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>57,363,709</t>
+          <t>57,580,508</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>206,979,133</t>
+          <t>107,380,712</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>107,181,667</t>
+          <t>207,511,518</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>504,196,854</t>
+          <t>505,213,560</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>239,746,479</t>
+          <t>240,375,078</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>6,945,471</t>
+          <t>6,976,330</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1007,29 +1007,29 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>7,998,942</t>
+          <t>8,020,803</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,318</t>
+          <t>257,169,701</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,132 +1041,132 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>67,132,703</t>
+          <t>330,771,399</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>256,490,070</t>
+          <t>2,268,602</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>329,898,016</t>
+          <t>279,417,609</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,255,444</t>
+          <t>67,309,674</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>278,819,209</t>
+          <t>83,013,527</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>82,289,373</t>
+          <t>16,579,426</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1183,29 +1183,29 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>24,756,450</t>
+          <t>24,822,496</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>342,206,115</t>
+          <t>14,685,207</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>14,645,949</t>
+          <t>342,933,520</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1249,51 +1249,51 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,196,364</t>
+          <t>1,205,520</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>16,548,626</t>
+          <t>65,701,369</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>65,528,401</t>
+          <t>42,585,405</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>42,448,403</t>
+          <t>990</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,83 +1327,83 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>107,233,223</t>
+          <t>2,041,093</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>243,047,501</t>
+          <t>1,241,673</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>2,037,320</t>
+          <t>107,516,884</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,237,440</t>
+          <t>243,691,107</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>7,458,784</t>
+          <t>7,478,644</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>199,496,810</t>
+          <t>200,025,335</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>1,743,220</t>
+          <t>1,747,454</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>1,711,836</t>
+          <t>23,658,606</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>3,879,630</t>
+          <t>3,889,791</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,39 +1525,39 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>23,595,716</t>
+          <t>1,715,993</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,890,545</t>
+          <t>668</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,132 +1569,132 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>4,647,920</t>
+          <t>1,896,010</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>227,174,127</t>
+          <t>4,656,544</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>10,005,031</t>
+          <t>227,775,165</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>23,574,490</t>
+          <t>10,031,714</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>38,303,930</t>
+          <t>23,636,380</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>38,599,617</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>30,064,743</t>
+          <t>30,747,800</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>24,898,817</t>
+          <t>24,964,171</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>202607NYF</t>
+          <t>202608NYF</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,288</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,7 +1767,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>202608NYF</t>
+          <t>202607NYF</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>688</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
